--- a/MSM/WGNSSK and HAWG 2025/archive/sprat_main_tables.xlsx
+++ b/MSM/WGNSSK and HAWG 2025/archive/sprat_main_tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Age-structured-marine-fish-database\MSM\archive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Age-structured-marine-fish-database\MSM\WGNSSK and HAWG 2025\archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75046AAF-4A89-4E4F-88B6-6387DFD9C1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5D1604-308D-433A-A9C7-E8C7A76C9033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-16110" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-16110" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="11.2.2-catch" sheetId="3" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="FM test" sheetId="12" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'11.2.3-weight'!$A$1:$F$205</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11.6.3 Num quart long'!$A$1:$F$205</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -10819,6 +10820,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F205" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
